--- a/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
+++ b/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
@@ -573,8 +573,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Sede legale Zagabria; rete negozi professionali utensili (Makita, Bosch, Milwaukee, DeWalt); vende aspiratori industriali (es. Makita VC3011L). Indirizzo filiale discordante tra fonti. Telefono/email diretti filiale non verificati, lasciati vuoti.</t>
@@ -612,7 +610,6 @@
           <t>072 44 66 22</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Catena nazionale bricolage/casa e giardino; vende aspiratori industriali a batteria/bagnato-asciutto (es. Einhell). Include centro vendita Vukovar (stessa catena). Non specializzata Cleaning B2B.</t>
@@ -662,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
+++ b/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Distributore specializzato macchine/attrezzature pulizia professionale (lavasciuga, aspiratori, monospazzole) e prodotti chimici; sede legale Zagabria ma copertura commerciale documentata su Vukovarsko-srijemska tramite agente di zona nominativo.</t>
+          <t>Distributore specializzato macchine/attrezzature pulizia professionale (lavasciuga, aspiratori, monospazzole) e prodotti chimici; sede legale Zagabria ma copertura commerciale documentata su Vukovarsko-srijemska tramite agente di zona nominativo. [DUPLICATO — vedi anche: 2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
+++ b/output/2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filiale locale catena nazionale elettronica/elettrodomestici HGSPOT; sito nazionale ha categoria 'Industrijski usisavaci' (aspiratori industriali). P.IVA non confermata da registro imprese.</t>
+          <t>Filiale locale catena nazionale elettronica/elettrodomestici HGSPOT; sito nazionale ha categoria 'Industrijski usisavaci' (aspiratori industriali). P.IVA non confermata da registro imprese. [DUPLICATO — vedi anche: 2026-09-15_20_Croazia_Brodsko-posavska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede legale Zagabria; rete negozi professionali utensili (Makita, Bosch, Milwaukee, DeWalt); vende aspiratori industriali (es. Makita VC3011L). Indirizzo filiale discordante tra fonti. Telefono/email diretti filiale non verificati, lasciati vuoti.</t>
+          <t>Sede legale Zagabria; rete negozi professionali utensili (Makita, Bosch, Milwaukee, DeWalt); vende aspiratori industriali (es. Makita VC3011L). Indirizzo filiale discordante tra fonti. Telefono/email diretti filiale non verificati, lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Catena nazionale bricolage/casa e giardino; vende aspiratori industriali a batteria/bagnato-asciutto (es. Einhell). Include centro vendita Vukovar (stessa catena). Non specializzata Cleaning B2B.</t>
+          <t>Catena nazionale bricolage/casa e giardino; vende aspiratori industriali a batteria/bagnato-asciutto (es. Einhell). Include centro vendita Vukovar (stessa catena). Non specializzata Cleaning B2B. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
